--- a/www/download/IND.surplus_value.empe_ms.r.pc.rpO1.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>325.83</t>
+          <t>3.25826079166601</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>316.38</t>
+          <t>3.16382769578375</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>309.32</t>
+          <t>3.09318257159866</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>310.7</t>
+          <t>3.10704802683107</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>326.72</t>
+          <t>3.26715110273724</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>321.88</t>
+          <t>3.2188352973533</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>313.79</t>
+          <t>3.13792223222347</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>322.17</t>
+          <t>3.22172051526841</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>336.3</t>
+          <t>3.36299402901279</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>326.33</t>
+          <t>3.26334560289826</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>332.75</t>
+          <t>3.32747271467133</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>323.92</t>
+          <t>3.23924228422054</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>314.02</t>
+          <t>3.14022033726132</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>303.81</t>
+          <t>3.03806977886596</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>295.54</t>
+          <t>2.95543793490168</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>352.86</t>
+          <t>3.52862229892583</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>341.46</t>
+          <t>3.41461609458868</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>330.72</t>
+          <t>3.30721195978158</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>328.35</t>
+          <t>3.2834689856988</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>345.38</t>
+          <t>3.45378830504235</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>337.64</t>
+          <t>3.37637256324731</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>326.78</t>
+          <t>3.26779653536426</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>334.18</t>
+          <t>3.34177637015696</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>362.83</t>
+          <t>3.62830317439473</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>342.82</t>
+          <t>3.42816434010312</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>343.69</t>
+          <t>3.43694384617567</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>334.66</t>
+          <t>3.34657433840743</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>322.04</t>
+          <t>3.22037303926455</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>313.28</t>
+          <t>3.13277660464457</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>306.61</t>
+          <t>3.06612725669408</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>376.32</t>
+          <t>3.76324068455269</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>3.62871582888102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>351.4</t>
+          <t>3.51402085184379</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>349.3</t>
+          <t>3.4930104267861</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>366.29</t>
+          <t>3.66294542079477</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>354.23</t>
+          <t>3.54229902034684</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>342.5</t>
+          <t>3.42499391370982</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>349.2</t>
+          <t>3.49196498741015</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>378.05</t>
+          <t>3.78048537427135</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>352.1</t>
+          <t>3.52096357597215</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>356.06</t>
+          <t>3.56060148880021</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>348.71</t>
+          <t>3.48709955608434</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>332.9</t>
+          <t>3.32901704695805</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>325.79</t>
+          <t>3.25785858209853</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>318.33</t>
+          <t>3.18333853889</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>308.65</t>
+          <t>3.08653954945979</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>297.26</t>
+          <t>2.97263217731629</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>286.84</t>
+          <t>2.86837956518391</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>292.21</t>
+          <t>2.92210583318951</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>309.15</t>
+          <t>3.09154111630277</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>301.36</t>
+          <t>3.01358581272916</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>292.01</t>
+          <t>2.92012508507781</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>299.77</t>
+          <t>2.99769944417919</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>470.96</t>
+          <t>4.70960685968039</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>312.48</t>
+          <t>3.12478583550846</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>319.26</t>
+          <t>3.19260569922156</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>306.97</t>
+          <t>3.06970637331579</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>302.68</t>
+          <t>3.02681604586821</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>304.86</t>
+          <t>3.04864200972948</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>294.19</t>
+          <t>2.94187960178339</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>376.73</t>
+          <t>3.76728950720739</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>370.18</t>
+          <t>3.70182367167653</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>364.33</t>
+          <t>3.64327924230533</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>370.85</t>
+          <t>3.70853562239997</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>395.71</t>
+          <t>3.95714176307784</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>385.28</t>
+          <t>3.852824118362</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>379.82</t>
+          <t>3.79819552047183</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>395.64</t>
+          <t>3.95640974048312</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>413.42</t>
+          <t>4.13422162478796</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>401.77</t>
+          <t>4.01767058544832</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>409.5</t>
+          <t>4.0949654431143</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>405.31</t>
+          <t>4.05312964319434</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>400.36</t>
+          <t>4.00364137424641</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>392.11</t>
+          <t>3.92110928272434</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>385.93</t>
+          <t>3.85925619262483</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>361.29</t>
+          <t>3.6128574216259</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>354.41</t>
+          <t>3.54413194546661</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>348.02</t>
+          <t>3.48021920452053</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>346.75</t>
+          <t>3.46748192040563</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>362.12</t>
+          <t>3.62121327020607</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>352.56</t>
+          <t>3.5256048508746</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>342.35</t>
+          <t>3.42353774429275</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>350.44</t>
+          <t>3.50440044653179</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>361.79</t>
+          <t>3.61792825742098</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>349.54</t>
+          <t>3.49539882554242</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>352.15</t>
+          <t>3.5214775274161</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>344.65</t>
+          <t>3.44650684669139</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>333.39</t>
+          <t>3.33388878199605</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>322.77</t>
+          <t>3.22766932769443</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>314.67</t>
+          <t>3.14671402695979</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>341.27</t>
+          <t>3.41265408998639</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>326.46</t>
+          <t>3.26455934822251</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>314.69</t>
+          <t>3.14686989073813</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>311.7</t>
+          <t>3.11698484673137</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>323.9</t>
+          <t>3.23903706881814</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>314.71</t>
+          <t>3.14706712458188</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>303.12</t>
+          <t>3.03124561610057</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>308.43</t>
+          <t>3.08427725647698</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>322.75</t>
+          <t>3.22745009996453</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>312.93</t>
+          <t>3.12932776067384</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>317.52</t>
+          <t>3.17524484678916</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>311.21</t>
+          <t>3.11213265571638</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>303.77</t>
+          <t>3.03768905391853</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>294.39</t>
+          <t>2.94391760158119</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>286.67</t>
+          <t>2.86671792113306</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>404.58</t>
+          <t>4.04583380548295</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>391.34</t>
+          <t>3.91342090347299</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>373.57</t>
+          <t>3.73570435018472</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>365.33</t>
+          <t>3.65329977420272</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>380.35</t>
+          <t>3.80349198428458</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>370.94</t>
+          <t>3.70943784742365</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>358.54</t>
+          <t>3.58537733366708</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>364.29</t>
+          <t>3.64291109591663</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>388.43</t>
+          <t>3.88430511391483</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>369.31</t>
+          <t>3.69308744262681</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>373.49</t>
+          <t>3.7348723027549</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>366.51</t>
+          <t>3.66507309838528</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>355.61</t>
+          <t>3.55611519259192</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>340.68</t>
+          <t>3.40675977577921</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>333.14</t>
+          <t>3.33135865676762</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>376.68</t>
+          <t>3.76681342900052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>362.42</t>
+          <t>3.62417452824299</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>350.73</t>
+          <t>3.50731083674518</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>348.29</t>
+          <t>3.48292243042001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>363.7</t>
+          <t>3.6369853013861</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>357.26</t>
+          <t>3.57258995470178</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>347.08</t>
+          <t>3.47083848383801</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>355.84</t>
+          <t>3.55835991329207</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>368.31</t>
+          <t>3.68311783800302</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>359.56</t>
+          <t>3.59556922041663</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>364.16</t>
+          <t>3.64158095678412</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>356.04</t>
+          <t>3.56038416517085</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>347.54</t>
+          <t>3.47536265791118</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>335.76</t>
+          <t>3.35761141589216</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>330.07</t>
+          <t>3.30066709550702</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>380.21</t>
+          <t>3.80211877297636</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>365.75</t>
+          <t>3.65751064229747</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>353.7</t>
+          <t>3.53697068914566</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>357.32</t>
+          <t>3.57322244461027</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>366.75</t>
+          <t>3.66747001037119</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>357.42</t>
+          <t>3.57418203760671</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>347.1</t>
+          <t>3.47099136409001</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>360.81</t>
+          <t>3.60808712562344</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>381.49</t>
+          <t>3.81492905777105</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>361.33</t>
+          <t>3.61329931986744</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>365.97</t>
+          <t>3.65970872578335</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>362.19</t>
+          <t>3.62192280494786</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>356.7</t>
+          <t>3.5669868706075</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>347.33</t>
+          <t>3.47328859938736</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>338.45</t>
+          <t>3.38454387920456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>354.81</t>
+          <t>3.54810817537136</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>341.53</t>
+          <t>3.41532310751273</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>330.95</t>
+          <t>3.30947622553269</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>330.01</t>
+          <t>3.30007514520323</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>344.18</t>
+          <t>3.44183369397019</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>336.67</t>
+          <t>3.36672977625048</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>326.65</t>
+          <t>3.26645054755327</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>333.18</t>
+          <t>3.33183552461503</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>341.66</t>
+          <t>3.41657464150769</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>328.26</t>
+          <t>3.2826405524139</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>330.38</t>
+          <t>3.30379148522339</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>319.69</t>
+          <t>3.19689950551699</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>310.5</t>
+          <t>3.10503635127125</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>303.63</t>
+          <t>3.03625831082436</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>295.09</t>
+          <t>2.9509347498775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>369.05</t>
+          <t>3.69045248097475</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>357.8</t>
+          <t>3.57803732671138</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>347.41</t>
+          <t>3.47405229425956</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>345.86</t>
+          <t>3.45864355511783</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>361.22</t>
+          <t>3.61216938643981</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>353.1</t>
+          <t>3.53096454547507</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>343.77</t>
+          <t>3.43774769212697</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>351.36</t>
+          <t>3.51356876264131</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>403.4</t>
+          <t>4.03404394079395</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>347.57</t>
+          <t>3.47574564629621</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>350.06</t>
+          <t>3.5006273719884</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>338.34</t>
+          <t>3.38342350259775</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>333.8</t>
+          <t>3.33799238064904</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>320.32</t>
+          <t>3.20318279486358</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>313.81</t>
+          <t>3.13812660652043</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>4.39999637994001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>422.76</t>
+          <t>4.2276341212643</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>406.16</t>
+          <t>4.0616291710621</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>400.39</t>
+          <t>4.00387941594067</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>417.34</t>
+          <t>4.17340198991392</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>405.85</t>
+          <t>4.05853188311431</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>390.47</t>
+          <t>3.90467906181744</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>396.3</t>
+          <t>3.96299925579972</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>403.92</t>
+          <t>4.03917932470176</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>389.03</t>
+          <t>3.8903445872001</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>398.16</t>
+          <t>3.98158796921649</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>384.05</t>
+          <t>3.84054673424637</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>356.13</t>
+          <t>3.56133985196171</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>341.09</t>
+          <t>3.41085963156363</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>336.38</t>
+          <t>3.36382167247871</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>393.57</t>
+          <t>3.9357353220025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>378.66</t>
+          <t>3.78659873030267</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>365.76</t>
+          <t>3.65755947414291</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>361.09</t>
+          <t>3.6109363681139</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>380.6</t>
+          <t>3.80600589141659</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>371.93</t>
+          <t>3.71929279815329</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>356.77</t>
+          <t>3.56772889076513</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>364.76</t>
+          <t>3.6476115973384</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>375.18</t>
+          <t>3.75183788929322</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>371.14</t>
+          <t>3.71138496709742</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>377.01</t>
+          <t>3.77013353067011</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>369.38</t>
+          <t>3.69379412087691</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>370.52</t>
+          <t>3.70523513269537</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>364.66</t>
+          <t>3.64660070952497</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>356.7</t>
+          <t>3.56695183050294</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>392.91</t>
+          <t>3.92912572579614</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>379.79</t>
+          <t>3.79787212167379</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>361.54</t>
+          <t>3.61536225030962</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>364.28</t>
+          <t>3.64282267607651</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>379.17</t>
+          <t>3.79170759713889</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>374.26</t>
+          <t>3.74256104461494</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>363.11</t>
+          <t>3.63108040984055</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>367.43</t>
+          <t>3.67427422747505</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>396.4</t>
+          <t>3.96397219196689</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>360.27</t>
+          <t>3.60266109971136</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>362.19</t>
+          <t>3.62191115723243</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>351.31</t>
+          <t>3.51311084857638</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>344.11</t>
+          <t>3.44114833058475</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>335.03</t>
+          <t>3.3502806938248</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>329.21</t>
+          <t>3.29214993185368</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>380.71</t>
+          <t>3.80705492960141</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>373.88</t>
+          <t>3.73882535205606</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>362.62</t>
+          <t>3.62616154552461</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>363.7</t>
+          <t>3.63702219790741</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>381.87</t>
+          <t>3.81871398335734</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>379.51</t>
+          <t>3.79506657109954</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>366.98</t>
+          <t>3.66984920540456</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>377.02</t>
+          <t>3.77016669364873</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>391.23</t>
+          <t>3.91225825568978</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>376.88</t>
+          <t>3.76877515627261</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>382.74</t>
+          <t>3.82744890584089</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>374.24</t>
+          <t>3.74238375309216</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>363.74</t>
+          <t>3.63741763954978</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>361.74</t>
+          <t>3.61744055259243</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>349.32</t>
+          <t>3.49317239255813</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>456.52</t>
+          <t>4.5652201600018</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>426.41</t>
+          <t>4.2640502664115</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>401.53</t>
+          <t>4.0152819836841</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>387.11</t>
+          <t>3.87108045968753</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>388.77</t>
+          <t>3.88769415946702</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>369.31</t>
+          <t>3.69310028277353</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>359.67</t>
+          <t>3.59670781598832</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>369.31</t>
+          <t>3.69305967824894</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>400.24</t>
+          <t>4.00243514556709</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>365.51</t>
+          <t>3.65507195592602</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>364.39</t>
+          <t>3.64389602525932</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>353.51</t>
+          <t>3.53512086435049</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>343.02</t>
+          <t>3.43022919223004</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>343.77</t>
+          <t>3.43773672653127</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>334.69</t>
+          <t>3.346891674597</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>401.7</t>
+          <t>4.01696635687475</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>387.75</t>
+          <t>3.87746768910378</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>375.72</t>
+          <t>3.7572145094885</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>374.4</t>
+          <t>3.74398434597606</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>402.94</t>
+          <t>4.02939747132105</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>390.9</t>
+          <t>3.90898402534954</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>376.63</t>
+          <t>3.76633181949022</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>386.94</t>
+          <t>3.86943248036802</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>421.31</t>
+          <t>4.21309095672831</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>400.7</t>
+          <t>4.00695917749684</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>407.37</t>
+          <t>4.07373582204678</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>3.99003308761369</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>391.58</t>
+          <t>3.91579146739299</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>384.52</t>
+          <t>3.84521692045796</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>3.79000549486575</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>246.06</t>
+          <t>2.46057273125038</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>249.58</t>
+          <t>2.49576430566495</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>223.24</t>
+          <t>2.2324263579741</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>232.76</t>
+          <t>2.32760149223596</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>249.45</t>
+          <t>2.49446352971949</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>280.32</t>
+          <t>2.80320050371307</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>258.55</t>
+          <t>2.58550405993007</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>256.86</t>
+          <t>2.56864480984294</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>290.46</t>
+          <t>2.90461021783255</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>256.47</t>
+          <t>2.56474021823778</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>312.59</t>
+          <t>3.12594805897303</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>337.42</t>
+          <t>3.37422279984666</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>340.08</t>
+          <t>3.40076442012055</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>325.97</t>
+          <t>3.25968925180904</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>325.78</t>
+          <t>3.25781139404624</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>327.12</t>
+          <t>3.27119192090781</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>315.44</t>
+          <t>3.1544056891709</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>306.71</t>
+          <t>3.06705354169366</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>307.79</t>
+          <t>3.0778747663194</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>322.73</t>
+          <t>3.22726916248107</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>320.35</t>
+          <t>3.20352345824335</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>315.47</t>
+          <t>3.15467994538164</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>327.96</t>
+          <t>3.27963772849095</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>347.07</t>
+          <t>3.47065715777906</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>339.66</t>
+          <t>3.39663899571536</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>342.07</t>
+          <t>3.42065206251291</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>332.68</t>
+          <t>3.32681187168767</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>322.1</t>
+          <t>3.22102173438172</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>311.67</t>
+          <t>3.11666794229365</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>303.07</t>
+          <t>3.03070206141613</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>370.51</t>
+          <t>3.70512510016211</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>352.09</t>
+          <t>3.52093562424385</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>336.53</t>
+          <t>3.36534800427526</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>330.17</t>
+          <t>3.30165482518273</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>340.19</t>
+          <t>3.40188060882213</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>329.82</t>
+          <t>3.29815616018022</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>319.59</t>
+          <t>3.19591307846841</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>328.34</t>
+          <t>3.28343922113721</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>345.34</t>
+          <t>3.45342120356136</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>332.32</t>
+          <t>3.32319019553289</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>364.98</t>
+          <t>3.64975629318188</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>371.53</t>
+          <t>3.71530432109761</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>374.22</t>
+          <t>3.74216967265257</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>351.65</t>
+          <t>3.51650103483383</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>344.24</t>
+          <t>3.44242617831197</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>390.9</t>
+          <t>3.90899275428949</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>370.86</t>
+          <t>3.70864116814406</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>354.04</t>
+          <t>3.54039921311531</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>344.91</t>
+          <t>3.44907360178454</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>362.18</t>
+          <t>3.62178187018181</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>357.81</t>
+          <t>3.57807682490353</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>332.43</t>
+          <t>3.3242901712451</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>332.04</t>
+          <t>3.32037859769667</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>381.31</t>
+          <t>3.81310298512541</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>328.03</t>
+          <t>3.28031022959938</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>328.28</t>
+          <t>3.28276337967512</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>317.13</t>
+          <t>3.17126082988157</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>305.39</t>
+          <t>3.05392316226097</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>304.89</t>
+          <t>3.04890358376569</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>297.25</t>
+          <t>2.972516072788</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>391.55</t>
+          <t>3.91547868208457</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>377.66</t>
+          <t>3.77661861989295</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>365.32</t>
+          <t>3.65315581243067</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>364.72</t>
+          <t>3.64724498751867</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>379.83</t>
+          <t>3.79825830124958</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>371.01</t>
+          <t>3.71008262254141</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>361.03</t>
+          <t>3.61025198963805</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>371.96</t>
+          <t>3.71963870931875</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>383.8</t>
+          <t>3.83800073787067</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>371.2</t>
+          <t>3.71200751434611</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>375.05</t>
+          <t>3.75045356688834</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>365.56</t>
+          <t>3.65563365797752</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>355.24</t>
+          <t>3.55241904974359</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>344.03</t>
+          <t>3.4403414140152</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>335.26</t>
+          <t>3.35257326778184</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>398.55</t>
+          <t>3.98546138956809</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>388.84</t>
+          <t>3.88844735477574</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>373.77</t>
+          <t>3.73770162008812</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>375.96</t>
+          <t>3.75964369191345</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>394.94</t>
+          <t>3.94938310938552</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>381.65</t>
+          <t>3.81649901724485</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>381.53</t>
+          <t>3.81526874149158</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>394.3</t>
+          <t>3.94304972289127</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>407.38</t>
+          <t>4.07382238524009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>393.32</t>
+          <t>3.93320636395679</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>412.61</t>
+          <t>4.1261016816263</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>403.15</t>
+          <t>4.03152161621974</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>392.4</t>
+          <t>3.92395304896605</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>380.63</t>
+          <t>3.80634540203501</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>370.89</t>
+          <t>3.70885944369883</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>432.78</t>
+          <t>4.3278479099173</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>418.83</t>
+          <t>4.18832803472843</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>403.36</t>
+          <t>4.03355097417681</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>400.3</t>
+          <t>4.0030380670755</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>415.57</t>
+          <t>4.15570516401004</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>405.09</t>
+          <t>4.05087829462119</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>391.02</t>
+          <t>3.91017685139151</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>397.98</t>
+          <t>3.97981540718109</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>404.92</t>
+          <t>4.04918587982942</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>401.93</t>
+          <t>4.01933424290641</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>407.03</t>
+          <t>4.07028129691362</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>393.95</t>
+          <t>3.93945089180317</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>380.1</t>
+          <t>3.80103931567067</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>374.53</t>
+          <t>3.74526795047385</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>372.37</t>
+          <t>3.7236792543103</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>330.6</t>
+          <t>3.30599270594898</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>317.61</t>
+          <t>3.17612280262701</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>308.66</t>
+          <t>3.08662969578348</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>315.65</t>
+          <t>3.15649651432393</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>338.97</t>
+          <t>3.38974740166151</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>337.55</t>
+          <t>3.37549968887347</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>325.04</t>
+          <t>3.25040098581324</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>332.16</t>
+          <t>3.32160010685773</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>369.54</t>
+          <t>3.69541396048293</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>342.85</t>
+          <t>3.42850417493477</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>349.57</t>
+          <t>3.4956701613679</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>338.34</t>
+          <t>3.38342174345246</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>331.21</t>
+          <t>3.31210029010098</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>323.1</t>
+          <t>3.23100984311538</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>329.83</t>
+          <t>3.29831688784713</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>434.1</t>
+          <t>4.34104353432228</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>417.99</t>
+          <t>4.17991943953952</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>401.91</t>
+          <t>4.01907499714247</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>397.6</t>
+          <t>3.97596795673717</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>414.31</t>
+          <t>4.14314621884333</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>405.65</t>
+          <t>4.05652805814889</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>389.57</t>
+          <t>3.89570791184148</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>396.83</t>
+          <t>3.96832328596602</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>399.96</t>
+          <t>3.99955068512572</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>393.15</t>
+          <t>3.93154231900156</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>391.17</t>
+          <t>3.91174875411893</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>383.04</t>
+          <t>3.83037585617222</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>373.94</t>
+          <t>3.73939741906442</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>390.72</t>
+          <t>3.90720391168235</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>392.6</t>
+          <t>3.92596854756529</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>302.56</t>
+          <t>3.02555583525283</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>287.96</t>
+          <t>2.87964704083736</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>282.92</t>
+          <t>2.82921609657138</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>281.09</t>
+          <t>2.81094477571745</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>292.67</t>
+          <t>2.92670505694948</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>284.28</t>
+          <t>2.8427895993578</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>278.22</t>
+          <t>2.78218922882081</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>285.94</t>
+          <t>2.85940177305714</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>301.02</t>
+          <t>3.01021586578456</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>291.75</t>
+          <t>2.91749859185635</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>282.17</t>
+          <t>2.82171646702684</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>276.23</t>
+          <t>2.76234831122074</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>267.13</t>
+          <t>2.67126971774573</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>255.26</t>
+          <t>2.55258637944462</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>250.24</t>
+          <t>2.5023516302507</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>330.17</t>
+          <t>3.30169446328992</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>321.82</t>
+          <t>3.21815264563152</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>310.47</t>
+          <t>3.10472898793577</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>306.5</t>
+          <t>3.06498848570569</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>317.28</t>
+          <t>3.17275489759823</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>308.65</t>
+          <t>3.08648195034501</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>302.01</t>
+          <t>3.02014400491933</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>306.82</t>
+          <t>3.06823597619699</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>463.3</t>
+          <t>4.6330035979314</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>320.5</t>
+          <t>3.20502068103571</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>328.51</t>
+          <t>3.28512846126454</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>318.17</t>
+          <t>3.1816882813706</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.15607849028391</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>300.9</t>
+          <t>3.00899489990929</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>299.59</t>
+          <t>2.99585064589974</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>357.18</t>
+          <t>3.5717972569861</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>342.84</t>
+          <t>3.42836464485765</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>337.14</t>
+          <t>3.37139792416807</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>335.42</t>
+          <t>3.35422804863335</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>358.05</t>
+          <t>3.58049454626387</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>340.73</t>
+          <t>3.40734941518927</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>330.32</t>
+          <t>3.30323746373205</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>340.3</t>
+          <t>3.40301825666035</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>378.33</t>
+          <t>3.78328402465623</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>349.41</t>
+          <t>3.49409939543916</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>356.58</t>
+          <t>3.5657775233261</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>347.97</t>
+          <t>3.47970750156999</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>328.38</t>
+          <t>3.28375503299014</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>328.53</t>
+          <t>3.28529936718651</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>320.27</t>
+          <t>3.20272566407948</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>385.8</t>
+          <t>3.85798483185412</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>371.38</t>
+          <t>3.71377254984281</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>360.17</t>
+          <t>3.60165494148052</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>358.12</t>
+          <t>3.58115408667379</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>373.57</t>
+          <t>3.73571062997009</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>365.08</t>
+          <t>3.65075626199591</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>356.75</t>
+          <t>3.56750231026184</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>371.86</t>
+          <t>3.71859742037474</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>392.79</t>
+          <t>3.92794677045729</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>382.39</t>
+          <t>3.82386726675845</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>388.11</t>
+          <t>3.88114759430835</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>379.29</t>
+          <t>3.79290649191128</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>371.4</t>
+          <t>3.71399850308858</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>354.71</t>
+          <t>3.54705789543529</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>348.99</t>
+          <t>3.48985613713279</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>340.95</t>
+          <t>3.40952508177977</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>328.28</t>
+          <t>3.28275121972692</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>316.15</t>
+          <t>3.16151684484268</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>312.32</t>
+          <t>3.12320400525183</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>324.96</t>
+          <t>3.2496478751856</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>316.95</t>
+          <t>3.16953960507233</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>307.25</t>
+          <t>3.07252162792308</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>312.97</t>
+          <t>3.1296538957426</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>475.21</t>
+          <t>4.75209497453801</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>325.11</t>
+          <t>3.2511348310085</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>331.55</t>
+          <t>3.3155167034741</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>320.45</t>
+          <t>3.20446061174248</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>315.48</t>
+          <t>3.15475676958767</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>310.12</t>
+          <t>3.10117296866143</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>301.97</t>
+          <t>3.01973192060357</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>298.78</t>
+          <t>2.98782976822175</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>286.06</t>
+          <t>2.86058771556959</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>282.15</t>
+          <t>2.82147419389527</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>2.7599505025664</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>302.9</t>
+          <t>3.02901161923549</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>289.95</t>
+          <t>2.89947950889056</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>274.42</t>
+          <t>2.74417411910028</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>282.92</t>
+          <t>2.82923374266394</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>461.98</t>
+          <t>4.61975835589907</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>297.91</t>
+          <t>2.97914759702917</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>304.73</t>
+          <t>3.04729944606789</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>295.86</t>
+          <t>2.95864681131145</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>289.76</t>
+          <t>2.89755157122397</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>282.45</t>
+          <t>2.82451697056736</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>275.84</t>
+          <t>2.75842612243822</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>386.8</t>
+          <t>3.86797615104304</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>372.97</t>
+          <t>3.72968423035978</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>361.38</t>
+          <t>3.61377663098113</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>359.1</t>
+          <t>3.59102741581415</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>373.55</t>
+          <t>3.73547445353383</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>366.13</t>
+          <t>3.66134376392881</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>357.59</t>
+          <t>3.57593311495429</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>368.68</t>
+          <t>3.68678780946621</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>386.28</t>
+          <t>3.86275707450215</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>373.82</t>
+          <t>3.7381933972886</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>380.43</t>
+          <t>3.80426349686679</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>372.4</t>
+          <t>3.72401765326986</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>363.25</t>
+          <t>3.63250338393994</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>352.3</t>
+          <t>3.52297530592951</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>344.71</t>
+          <t>3.44714886940018</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>376.87</t>
+          <t>3.76872285771846</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>363.67</t>
+          <t>3.63667344931673</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>351.87</t>
+          <t>3.51872086945298</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>349.91</t>
+          <t>3.4991484707044</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>369.48</t>
+          <t>3.69481903261336</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>364.04</t>
+          <t>3.64043642633104</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>349.76</t>
+          <t>3.49762945535281</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>351.95</t>
+          <t>3.51945520228226</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>370.5</t>
+          <t>3.7050155943124</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>3.59948061787965</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>371.21</t>
+          <t>3.71206298027298</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>365.19</t>
+          <t>3.65186109930002</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>346.72</t>
+          <t>3.46721902139453</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>339.98</t>
+          <t>3.39976793819141</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>331.77</t>
+          <t>3.31770685926443</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>397.1</t>
+          <t>3.97103950676177</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>383.27</t>
+          <t>3.83267346418554</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>371.61</t>
+          <t>3.71607620745723</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>369.36</t>
+          <t>3.69357384648705</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>385.19</t>
+          <t>3.85191978665288</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>388.27</t>
+          <t>3.88267229880413</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>362.54</t>
+          <t>3.62540280882129</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>375.2</t>
+          <t>3.75201732651748</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>398.18</t>
+          <t>3.98176110112108</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>3.87998192454752</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>394.91</t>
+          <t>3.94910553457921</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>380.15</t>
+          <t>3.80154294862263</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>371.49</t>
+          <t>3.7149419948005</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>356.26</t>
+          <t>3.56264606613498</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>350.73</t>
+          <t>3.50730541266749</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>372.18</t>
+          <t>3.72184914611833</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>356.84</t>
+          <t>3.56837137367809</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>344.89</t>
+          <t>3.44888294569979</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>342.08</t>
+          <t>3.42082094704266</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>357.72</t>
+          <t>3.57720616641073</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>351.74</t>
+          <t>3.51737456969246</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>3.39995145360041</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>348.13</t>
+          <t>3.4813381280074</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>361.59</t>
+          <t>3.61590373929681</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>347.6</t>
+          <t>3.47603019489135</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>351.35</t>
+          <t>3.51351723699528</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>342.83</t>
+          <t>3.42827949030335</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>335.2</t>
+          <t>3.35199293141188</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>328.47</t>
+          <t>3.2847369013056</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>319.85</t>
+          <t>3.19849115749007</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>345.33</t>
+          <t>3.4533209931915</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>335.51</t>
+          <t>3.3551457343687</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>326.75</t>
+          <t>3.26753249161728</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>327.26</t>
+          <t>3.27262692817117</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>349.59</t>
+          <t>3.49593354289387</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>337.3</t>
+          <t>3.3730367180709</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>328.51</t>
+          <t>3.28512379595882</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>334.89</t>
+          <t>3.34886454445263</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>351.93</t>
+          <t>3.51932988663359</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>329.66</t>
+          <t>3.29663644052985</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>325.03</t>
+          <t>3.25026608242023</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>314.16</t>
+          <t>3.14155497894185</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>309.57</t>
+          <t>3.09565225198206</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>300.22</t>
+          <t>3.00218412297836</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>299.29</t>
+          <t>2.99286356556872</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>381.79</t>
+          <t>3.81787072903193</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>368.59</t>
+          <t>3.68587624425129</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>357.98</t>
+          <t>3.57984918994369</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>356.18</t>
+          <t>3.5618239117735</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>371.41</t>
+          <t>3.71405749909617</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>363.09</t>
+          <t>3.63087917440777</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>351.71</t>
+          <t>3.51708577128053</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>358.18</t>
+          <t>3.58181710843725</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>371.77</t>
+          <t>3.71771545568378</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>357.32</t>
+          <t>3.57317242371565</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>358.68</t>
+          <t>3.58675629279415</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>349.74</t>
+          <t>3.49739114035673</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>339.7</t>
+          <t>3.39695316316719</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>333.98</t>
+          <t>3.3397897493248</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>323.16</t>
+          <t>3.23163982596322</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>407.45</t>
+          <t>4.07454035632438</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>393.64</t>
+          <t>3.93636795638414</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>387.36</t>
+          <t>3.87363922148337</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>385.91</t>
+          <t>3.85911814238171</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>398.17</t>
+          <t>3.98166009200512</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>401.44</t>
+          <t>4.01439828916761</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>389.2</t>
+          <t>3.89196518253142</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>393.21</t>
+          <t>3.93205369833134</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>408.75</t>
+          <t>4.08746212368928</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>401.78</t>
+          <t>4.01783232904317</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>404.86</t>
+          <t>4.04858681354354</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>400.87</t>
+          <t>4.00873210303346</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>384.47</t>
+          <t>3.84474614544299</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>376.86</t>
+          <t>3.76858546226346</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>368.39</t>
+          <t>3.68394170851918</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>386.92</t>
+          <t>3.86920809932848</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>372.66</t>
+          <t>3.72655579297538</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>361.22</t>
+          <t>3.61224381878103</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>359.74</t>
+          <t>3.59743873141907</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>375.4</t>
+          <t>3.75400641626665</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>367.98</t>
+          <t>3.67978638313392</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>355.76</t>
+          <t>3.5576138284824</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>363.35</t>
+          <t>3.63348150196631</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>387.17</t>
+          <t>3.87174222325787</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>364.63</t>
+          <t>3.64631395261499</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>369.39</t>
+          <t>3.69393707819979</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>360.67</t>
+          <t>3.60669563611433</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>351.11</t>
+          <t>3.51109966380433</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>339.57</t>
+          <t>3.39570435931419</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>334.19</t>
+          <t>3.34186545719055</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>388.84</t>
+          <t>3.88843920077044</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>375.22</t>
+          <t>3.75221839467526</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>365.19</t>
+          <t>3.65192462933106</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>365.03</t>
+          <t>3.65033962875793</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>379.04</t>
+          <t>3.79035687385083</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>375.41</t>
+          <t>3.75412394955774</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>363.98</t>
+          <t>3.63980951961713</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>370.6</t>
+          <t>3.70600724898331</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>388.56</t>
+          <t>3.88561946081681</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>372.36</t>
+          <t>3.72356091636825</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>376.08</t>
+          <t>3.76075839702692</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>368.79</t>
+          <t>3.68788946553967</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>356.62</t>
+          <t>3.56616495394837</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>346.72</t>
+          <t>3.46716508164478</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>338.67</t>
+          <t>3.38672112755226</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
